--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="158">
   <si>
     <t>Property</t>
   </si>
@@ -478,9 +478,6 @@
   </si>
   <si>
     <t>1.2.840.10008.5.1.4.1.1.88.59</t>
-  </si>
-  <si>
-    <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
   </si>
   <si>
     <t>http://dicom.nema.org/resources/ontology/DCMUID</t>
@@ -1337,9 +1334,7 @@
       <c r="A2" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1354,7 +1349,7 @@
         <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1381,10 +1376,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -1400,7 +1395,7 @@
         <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="159">
   <si>
     <t>Property</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>1.2.840.10008.5.1.4.1.1.88.59</t>
+  </si>
+  <si>
+    <t>Key Object Selection Document Storage</t>
   </si>
   <si>
     <t>http://dicom.nema.org/resources/ontology/DCMUID</t>
@@ -1334,7 +1337,9 @@
       <c r="A2" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>154</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1349,7 +1354,7 @@
         <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1376,10 +1381,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -1395,7 +1400,7 @@
         <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
